--- a/artfynd/A 37259-2024 artfynd.xlsx
+++ b/artfynd/A 37259-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113175421</v>
+        <v>113175422</v>
       </c>
       <c r="B2" t="n">
-        <v>56470</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +709,14 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -762,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,15 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113175422</v>
+        <v>113175421</v>
       </c>
       <c r="B3" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,14 +832,10 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -890,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 37259-2024 artfynd.xlsx
+++ b/artfynd/A 37259-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113175422</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,8 +924,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113175421</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>